--- a/Team-Data/2014-15/3-18-2014-15.xlsx
+++ b/Team-Data/2014-15/3-18-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,52 +728,52 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E2" t="n">
         <v>53</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
-        <v>0.779</v>
+        <v>0.791</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J2" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K2" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L2" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="N2" t="n">
         <v>0.383</v>
       </c>
       <c r="O2" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.778</v>
+        <v>0.776</v>
       </c>
       <c r="R2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="S2" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T2" t="n">
         <v>40.7</v>
@@ -733,16 +800,16 @@
         <v>20.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.5</v>
+        <v>102.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
@@ -754,16 +821,16 @@
         <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK2" t="n">
         <v>4</v>
       </c>
       <c r="AL2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
         <v>7</v>
@@ -772,10 +839,10 @@
         <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
         <v>6</v>
@@ -784,7 +851,7 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
@@ -793,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW2" t="n">
         <v>5</v>
@@ -802,13 +869,13 @@
         <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ2" t="n">
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -843,94 +910,94 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3" t="n">
         <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>0.448</v>
+        <v>0.455</v>
       </c>
       <c r="H3" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="J3" t="n">
-        <v>88.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.442</v>
+        <v>0.44</v>
       </c>
       <c r="L3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M3" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.333</v>
+        <v>0.331</v>
       </c>
       <c r="O3" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.749</v>
+        <v>0.752</v>
       </c>
       <c r="R3" t="n">
         <v>11.2</v>
       </c>
       <c r="S3" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T3" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U3" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="V3" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W3" t="n">
         <v>8</v>
       </c>
       <c r="X3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>101</v>
+        <v>100.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH3" t="n">
         <v>11</v>
@@ -951,13 +1018,13 @@
         <v>12</v>
       </c>
       <c r="AN3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AO3" t="n">
         <v>28</v>
       </c>
       <c r="AP3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ3" t="n">
         <v>18</v>
@@ -966,7 +1033,7 @@
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
         <v>13</v>
@@ -975,25 +1042,25 @@
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
         <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
         <v>29</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" t="n">
         <v>27</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>0.409</v>
+        <v>0.415</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1055,7 +1122,7 @@
         <v>20.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.324</v>
+        <v>0.325</v>
       </c>
       <c r="O4" t="n">
         <v>16.3</v>
@@ -1064,22 +1131,22 @@
         <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.741</v>
+        <v>0.742</v>
       </c>
       <c r="R4" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S4" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T4" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U4" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
@@ -1094,16 +1161,16 @@
         <v>19.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB4" t="n">
         <v>96.59999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.6</v>
+        <v>-3.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
@@ -1121,13 +1188,13 @@
         <v>20</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM4" t="n">
         <v>20</v>
@@ -1151,34 +1218,34 @@
         <v>20</v>
       </c>
       <c r="AT4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU4" t="n">
         <v>27</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
         <v>24</v>
       </c>
       <c r="AX4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB4" t="n">
         <v>23</v>
       </c>
       <c r="BC4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -1285,19 +1352,19 @@
         <v>-2.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="n">
         <v>26</v>
@@ -1324,7 +1391,7 @@
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR5" t="n">
         <v>25</v>
@@ -1336,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1345,10 +1412,10 @@
         <v>30</v>
       </c>
       <c r="AX5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
         <v>4</v>
@@ -1360,7 +1427,7 @@
         <v>28</v>
       </c>
       <c r="BC5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
         <v>28</v>
       </c>
       <c r="G6" t="n">
-        <v>0.594</v>
+        <v>0.588</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
@@ -1413,31 +1480,31 @@
         <v>0.439</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M6" t="n">
         <v>22</v>
       </c>
       <c r="N6" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="O6" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P6" t="n">
         <v>25.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.786</v>
+        <v>0.784</v>
       </c>
       <c r="R6" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S6" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
       <c r="T6" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="U6" t="n">
         <v>21.5</v>
@@ -1452,10 +1519,10 @@
         <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AA6" t="n">
         <v>21.4</v>
@@ -1464,13 +1531,13 @@
         <v>100.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
         <v>11</v>
@@ -1479,7 +1546,7 @@
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI6" t="n">
         <v>23</v>
@@ -1503,13 +1570,13 @@
         <v>2</v>
       </c>
       <c r="AP6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
         <v>6</v>
@@ -1527,19 +1594,19 @@
         <v>29</v>
       </c>
       <c r="AX6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA6" t="n">
         <v>5</v>
       </c>
       <c r="BB6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -1571,46 +1638,46 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F7" t="n">
         <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>0.629</v>
+        <v>0.623</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J7" t="n">
         <v>82.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M7" t="n">
         <v>26.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.364</v>
+        <v>0.362</v>
       </c>
       <c r="O7" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P7" t="n">
         <v>24.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.757</v>
+        <v>0.759</v>
       </c>
       <c r="R7" t="n">
         <v>11.1</v>
@@ -1622,7 +1689,7 @@
         <v>42.8</v>
       </c>
       <c r="U7" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V7" t="n">
         <v>14</v>
@@ -1643,16 +1710,16 @@
         <v>20.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>103.6</v>
+        <v>103.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
@@ -1661,16 +1728,16 @@
         <v>8</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
         <v>14</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
@@ -1679,7 +1746,7 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO7" t="n">
         <v>6</v>
@@ -1688,28 +1755,28 @@
         <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR7" t="n">
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT7" t="n">
         <v>19</v>
       </c>
       <c r="AU7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
         <v>18</v>
       </c>
       <c r="AX7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -1756,13 +1823,13 @@
         <v>68</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>0.647</v>
+        <v>0.632</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1771,16 +1838,16 @@
         <v>39.5</v>
       </c>
       <c r="J8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K8" t="n">
         <v>0.462</v>
       </c>
       <c r="L8" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="N8" t="n">
         <v>0.354</v>
@@ -1792,22 +1859,22 @@
         <v>21.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.757</v>
+        <v>0.759</v>
       </c>
       <c r="R8" t="n">
         <v>10.5</v>
       </c>
       <c r="S8" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="V8" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="W8" t="n">
         <v>8.4</v>
@@ -1819,22 +1886,22 @@
         <v>3.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA8" t="n">
         <v>21.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.9</v>
+        <v>104.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
         <v>6</v>
@@ -1843,7 +1910,7 @@
         <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1861,25 +1928,25 @@
         <v>6</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO8" t="n">
         <v>20</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
         <v>19</v>
       </c>
       <c r="AS8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT8" t="n">
         <v>23</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>22</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1891,7 +1958,7 @@
         <v>8</v>
       </c>
       <c r="AX8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>23</v>
@@ -2025,7 +2092,7 @@
         <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AI9" t="n">
         <v>17</v>
@@ -2058,7 +2125,7 @@
         <v>4</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
         <v>6</v>
@@ -2067,7 +2134,7 @@
         <v>15</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW9" t="n">
         <v>17</v>
@@ -2088,7 +2155,7 @@
         <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E10" t="n">
         <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>0.353</v>
+        <v>0.358</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J10" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.425</v>
+        <v>0.427</v>
       </c>
       <c r="L10" t="n">
         <v>8.4</v>
@@ -2147,7 +2214,7 @@
         <v>25</v>
       </c>
       <c r="N10" t="n">
-        <v>0.334</v>
+        <v>0.335</v>
       </c>
       <c r="O10" t="n">
         <v>16.1</v>
@@ -2156,22 +2223,22 @@
         <v>22.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.709</v>
+        <v>0.707</v>
       </c>
       <c r="R10" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S10" t="n">
         <v>32.2</v>
       </c>
       <c r="T10" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="U10" t="n">
         <v>21.1</v>
       </c>
       <c r="V10" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W10" t="n">
         <v>7.7</v>
@@ -2180,7 +2247,7 @@
         <v>4.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z10" t="n">
         <v>19</v>
@@ -2189,13 +2256,13 @@
         <v>19.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>97.8</v>
+        <v>98</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2</v>
+        <v>-1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,13 +2274,13 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="n">
         <v>28</v>
@@ -2228,7 +2295,7 @@
         <v>22</v>
       </c>
       <c r="AO10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP10" t="n">
         <v>16</v>
@@ -2255,13 +2322,13 @@
         <v>16</v>
       </c>
       <c r="AX10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY10" t="n">
         <v>18</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA10" t="n">
         <v>22</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -2299,19 +2366,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.806</v>
+        <v>0.803</v>
       </c>
       <c r="H11" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I11" t="n">
         <v>41.4</v>
@@ -2320,7 +2387,7 @@
         <v>86.8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="L11" t="n">
         <v>10.7</v>
@@ -2329,16 +2396,16 @@
         <v>27.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0.394</v>
+        <v>0.393</v>
       </c>
       <c r="O11" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P11" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.77</v>
+        <v>0.772</v>
       </c>
       <c r="R11" t="n">
         <v>10.2</v>
@@ -2350,10 +2417,10 @@
         <v>44.5</v>
       </c>
       <c r="U11" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="V11" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W11" t="n">
         <v>9.5</v>
@@ -2365,7 +2432,7 @@
         <v>3.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA11" t="n">
         <v>18.9</v>
@@ -2374,10 +2441,10 @@
         <v>109.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2410,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP11" t="n">
         <v>26</v>
@@ -2434,7 +2501,7 @@
         <v>19</v>
       </c>
       <c r="AW11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX11" t="n">
         <v>1</v>
@@ -2443,7 +2510,7 @@
         <v>2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA11" t="n">
         <v>27</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -2481,46 +2548,46 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F12" t="n">
         <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.667</v>
+        <v>0.672</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J12" t="n">
-        <v>84.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L12" t="n">
         <v>11.5</v>
       </c>
       <c r="M12" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="P12" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.72</v>
+        <v>0.719</v>
       </c>
       <c r="R12" t="n">
         <v>12</v>
@@ -2538,46 +2605,46 @@
         <v>16.7</v>
       </c>
       <c r="W12" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="X12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>103</v>
+        <v>103.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
       </c>
       <c r="AF12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
         <v>19</v>
       </c>
       <c r="AJ12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2595,7 +2662,7 @@
         <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
@@ -2604,22 +2671,22 @@
         <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
@@ -2628,13 +2695,13 @@
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" t="n">
         <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>0.448</v>
+        <v>0.455</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2705,16 +2772,16 @@
         <v>0.765</v>
       </c>
       <c r="R13" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S13" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="T13" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="U13" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V13" t="n">
         <v>14.1</v>
@@ -2723,7 +2790,7 @@
         <v>6.2</v>
       </c>
       <c r="X13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y13" t="n">
         <v>4.9</v>
@@ -2735,31 +2802,31 @@
         <v>21.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>96.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH13" t="n">
         <v>18</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK13" t="n">
         <v>23</v>
@@ -2780,7 +2847,7 @@
         <v>23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
         <v>21</v>
@@ -2792,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="AU13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW13" t="n">
         <v>28</v>
@@ -2804,7 +2871,7 @@
         <v>18</v>
       </c>
       <c r="AY13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ13" t="n">
         <v>16</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -2845,22 +2912,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F14" t="n">
         <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>0.638</v>
+        <v>0.632</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J14" t="n">
         <v>83.3</v>
@@ -2869,19 +2936,19 @@
         <v>0.47</v>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="M14" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="O14" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P14" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="Q14" t="n">
         <v>0.713</v>
@@ -2890,10 +2957,10 @@
         <v>9.5</v>
       </c>
       <c r="S14" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T14" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U14" t="n">
         <v>24.4</v>
@@ -2917,22 +2984,22 @@
         <v>21.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>106</v>
+        <v>105.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH14" t="n">
         <v>29</v>
@@ -2941,13 +3008,13 @@
         <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK14" t="n">
         <v>2</v>
       </c>
       <c r="AL14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM14" t="n">
         <v>5</v>
@@ -2965,7 +3032,7 @@
         <v>28</v>
       </c>
       <c r="AR14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS14" t="n">
         <v>10</v>
@@ -2980,7 +3047,7 @@
         <v>2</v>
       </c>
       <c r="AW14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX14" t="n">
         <v>9</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E15" t="n">
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>0.262</v>
+        <v>0.258</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J15" t="n">
-        <v>86.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="K15" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O15" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="P15" t="n">
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.744</v>
+        <v>0.746</v>
       </c>
       <c r="R15" t="n">
         <v>11.7</v>
       </c>
       <c r="S15" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T15" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
       <c r="U15" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="n">
         <v>13.2</v>
@@ -3093,25 +3160,25 @@
         <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.2</v>
+        <v>99</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.9</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
@@ -3123,13 +3190,13 @@
         <v>15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK15" t="n">
         <v>24</v>
       </c>
       <c r="AL15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM15" t="n">
         <v>24</v>
@@ -3144,10 +3211,10 @@
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS15" t="n">
         <v>13</v>
@@ -3171,7 +3238,7 @@
         <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA15" t="n">
         <v>23</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3302,13 +3369,13 @@
         <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ16" t="n">
         <v>19</v>
       </c>
       <c r="AK16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3338,7 +3405,7 @@
         <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV16" t="n">
         <v>6</v>
@@ -3350,13 +3417,13 @@
         <v>23</v>
       </c>
       <c r="AY16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ16" t="n">
         <v>9</v>
       </c>
       <c r="BA16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB16" t="n">
         <v>18</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -3391,64 +3458,64 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F17" t="n">
         <v>36</v>
       </c>
       <c r="G17" t="n">
-        <v>0.463</v>
+        <v>0.455</v>
       </c>
       <c r="H17" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I17" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="J17" t="n">
-        <v>76.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L17" t="n">
         <v>6.9</v>
       </c>
       <c r="M17" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.341</v>
+        <v>0.338</v>
       </c>
       <c r="O17" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P17" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.743</v>
+        <v>0.744</v>
       </c>
       <c r="R17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T17" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="U17" t="n">
         <v>20.1</v>
       </c>
       <c r="V17" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W17" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X17" t="n">
         <v>4.3</v>
@@ -3457,19 +3524,19 @@
         <v>4.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2.2</v>
+        <v>-2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
@@ -3505,7 +3572,7 @@
         <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ17" t="n">
         <v>21</v>
@@ -3544,7 +3611,7 @@
         <v>27</v>
       </c>
       <c r="BC17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E18" t="n">
         <v>34</v>
       </c>
       <c r="F18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.507</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3600,13 +3667,13 @@
         <v>6.8</v>
       </c>
       <c r="M18" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.369</v>
+        <v>0.367</v>
       </c>
       <c r="O18" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P18" t="n">
         <v>21</v>
@@ -3624,19 +3691,19 @@
         <v>41.6</v>
       </c>
       <c r="U18" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V18" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="W18" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="X18" t="n">
         <v>4.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z18" t="n">
         <v>22</v>
@@ -3645,19 +3712,19 @@
         <v>20</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
       </c>
       <c r="AF18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
         <v>16</v>
@@ -3669,10 +3736,10 @@
         <v>18</v>
       </c>
       <c r="AJ18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL18" t="n">
         <v>23</v>
@@ -3684,13 +3751,13 @@
         <v>4</v>
       </c>
       <c r="AO18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP18" t="n">
         <v>25</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
         <v>24</v>
@@ -3699,13 +3766,13 @@
         <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW18" t="n">
         <v>4</v>
@@ -3714,10 +3781,10 @@
         <v>10</v>
       </c>
       <c r="AY18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA18" t="n">
         <v>20</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -3755,46 +3822,46 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E19" t="n">
         <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>0.209</v>
+        <v>0.212</v>
       </c>
       <c r="H19" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J19" t="n">
-        <v>84.3</v>
+        <v>84.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L19" t="n">
         <v>4.9</v>
       </c>
       <c r="M19" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="N19" t="n">
         <v>0.332</v>
       </c>
       <c r="O19" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="P19" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="R19" t="n">
         <v>12.2</v>
@@ -3803,7 +3870,7 @@
         <v>29.6</v>
       </c>
       <c r="T19" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U19" t="n">
         <v>22</v>
@@ -3818,28 +3885,28 @@
         <v>3.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
       </c>
       <c r="AF19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG19" t="n">
         <v>29</v>
@@ -3848,10 +3915,10 @@
         <v>25</v>
       </c>
       <c r="AI19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK19" t="n">
         <v>25</v>
@@ -3866,13 +3933,13 @@
         <v>24</v>
       </c>
       <c r="AO19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3884,10 +3951,10 @@
         <v>24</v>
       </c>
       <c r="AU19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW19" t="n">
         <v>9</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -3937,94 +4004,94 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F20" t="n">
         <v>30</v>
       </c>
       <c r="G20" t="n">
-        <v>0.545</v>
+        <v>0.552</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J20" t="n">
-        <v>82.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
         <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.362</v>
+        <v>0.36</v>
       </c>
       <c r="O20" t="n">
         <v>16.8</v>
       </c>
       <c r="P20" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.763</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
         <v>32.1</v>
       </c>
       <c r="T20" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="U20" t="n">
         <v>22</v>
       </c>
       <c r="V20" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W20" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z20" t="n">
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
         <v>99.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>21</v>
@@ -4036,7 +4103,7 @@
         <v>18</v>
       </c>
       <c r="AK20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
         <v>19</v>
@@ -4051,19 +4118,19 @@
         <v>16</v>
       </c>
       <c r="AP20" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AR20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS20" t="n">
         <v>17</v>
       </c>
       <c r="AT20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU20" t="n">
         <v>10</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -4197,19 +4264,19 @@
         <v>-8.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
         <v>29</v>
       </c>
       <c r="AF21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI21" t="n">
         <v>28</v>
@@ -4227,7 +4294,7 @@
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4239,7 +4306,7 @@
         <v>15</v>
       </c>
       <c r="AR21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
         <v>29</v>
@@ -4248,7 +4315,7 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV21" t="n">
         <v>16</v>
@@ -4257,7 +4324,7 @@
         <v>23</v>
       </c>
       <c r="AX21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY21" t="n">
         <v>8</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -4301,22 +4368,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E22" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F22" t="n">
         <v>30</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.552</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J22" t="n">
         <v>86.3</v>
@@ -4325,43 +4392,43 @@
         <v>0.445</v>
       </c>
       <c r="L22" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M22" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.331</v>
+        <v>0.332</v>
       </c>
       <c r="O22" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="P22" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.766</v>
+        <v>0.764</v>
       </c>
       <c r="R22" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S22" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="T22" t="n">
         <v>47.7</v>
       </c>
       <c r="U22" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V22" t="n">
         <v>14.9</v>
       </c>
       <c r="W22" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X22" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y22" t="n">
         <v>4.5</v>
@@ -4370,16 +4437,16 @@
         <v>22.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>103.1</v>
+        <v>102.8</v>
       </c>
       <c r="AC22" t="n">
         <v>2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
@@ -4391,13 +4458,13 @@
         <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK22" t="n">
         <v>19</v>
@@ -4409,16 +4476,16 @@
         <v>15</v>
       </c>
       <c r="AN22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4433,25 +4500,25 @@
         <v>22</v>
       </c>
       <c r="AV22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW22" t="n">
         <v>22</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>21</v>
       </c>
       <c r="AX22" t="n">
         <v>6</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ22" t="n">
         <v>29</v>
       </c>
       <c r="BA22" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BB22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC22" t="n">
         <v>11</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -4498,55 +4565,55 @@
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J23" t="n">
         <v>82.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O23" t="n">
         <v>14.1</v>
       </c>
       <c r="P23" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.724</v>
+        <v>0.723</v>
       </c>
       <c r="R23" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="U23" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="V23" t="n">
         <v>14.9</v>
       </c>
       <c r="W23" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>21</v>
@@ -4555,13 +4622,13 @@
         <v>18.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.8</v>
+        <v>-6</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4579,7 +4646,7 @@
         <v>16</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
         <v>13</v>
@@ -4591,7 +4658,7 @@
         <v>22</v>
       </c>
       <c r="AN23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4606,7 +4673,7 @@
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
         <v>27</v>
@@ -4615,19 +4682,19 @@
         <v>26</v>
       </c>
       <c r="AV23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F24" t="n">
         <v>52</v>
       </c>
       <c r="G24" t="n">
-        <v>0.235</v>
+        <v>0.224</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4683,28 +4750,28 @@
         <v>33.4</v>
       </c>
       <c r="J24" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K24" t="n">
-        <v>0.409</v>
+        <v>0.408</v>
       </c>
       <c r="L24" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M24" t="n">
         <v>25.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.317</v>
+        <v>0.316</v>
       </c>
       <c r="O24" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P24" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.673</v>
+        <v>0.674</v>
       </c>
       <c r="R24" t="n">
         <v>11.6</v>
@@ -4722,28 +4789,28 @@
         <v>18.2</v>
       </c>
       <c r="W24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z24" t="n">
         <v>21.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB24" t="n">
         <v>91</v>
       </c>
       <c r="AC24" t="n">
-        <v>-9.6</v>
+        <v>-9.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4776,7 +4843,7 @@
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP24" t="n">
         <v>11</v>
@@ -4785,7 +4852,7 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4794,7 +4861,7 @@
         <v>18</v>
       </c>
       <c r="AU24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,16 +4870,16 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>0.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
@@ -4952,7 +5019,7 @@
         <v>8</v>
       </c>
       <c r="AM25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN25" t="n">
         <v>13</v>
@@ -4970,13 +5037,13 @@
         <v>14</v>
       </c>
       <c r="AS25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT25" t="n">
         <v>17</v>
       </c>
       <c r="AU25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV25" t="n">
         <v>25</v>
@@ -4991,10 +5058,10 @@
         <v>5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E26" t="n">
         <v>44</v>
       </c>
       <c r="F26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G26" t="n">
-        <v>0.667</v>
+        <v>0.677</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
@@ -5047,10 +5114,10 @@
         <v>38.4</v>
       </c>
       <c r="J26" t="n">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="K26" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L26" t="n">
         <v>10.1</v>
@@ -5062,13 +5129,13 @@
         <v>0.364</v>
       </c>
       <c r="O26" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P26" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.797</v>
+        <v>0.801</v>
       </c>
       <c r="R26" t="n">
         <v>10.8</v>
@@ -5083,16 +5150,16 @@
         <v>22.2</v>
       </c>
       <c r="V26" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W26" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="X26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z26" t="n">
         <v>18.4</v>
@@ -5104,16 +5171,16 @@
         <v>102.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AE26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG26" t="n">
         <v>4</v>
@@ -5137,19 +5204,19 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
         <v>26</v>
       </c>
       <c r="AP26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5167,16 +5234,16 @@
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB26" t="n">
         <v>9</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -5211,46 +5278,46 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" t="n">
         <v>22</v>
       </c>
       <c r="F27" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G27" t="n">
-        <v>0.328</v>
+        <v>0.333</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J27" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K27" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L27" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M27" t="n">
         <v>16.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.331</v>
+        <v>0.333</v>
       </c>
       <c r="O27" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="P27" t="n">
         <v>29.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R27" t="n">
         <v>11.1</v>
@@ -5265,7 +5332,7 @@
         <v>19.9</v>
       </c>
       <c r="V27" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="W27" t="n">
         <v>6.5</v>
@@ -5277,7 +5344,7 @@
         <v>6.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA27" t="n">
         <v>24.3</v>
@@ -5286,10 +5353,10 @@
         <v>101</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.6</v>
+        <v>-4.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5301,7 +5368,7 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5349,13 +5416,13 @@
         <v>27</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY27" t="n">
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -5411,49 +5478,49 @@
         <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K28" t="n">
         <v>0.459</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.363</v>
+        <v>0.366</v>
       </c>
       <c r="O28" t="n">
-        <v>17.2</v>
+        <v>16.9</v>
       </c>
       <c r="P28" t="n">
-        <v>22.2</v>
+        <v>21.8</v>
       </c>
       <c r="Q28" t="n">
         <v>0.773</v>
       </c>
       <c r="R28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="U28" t="n">
         <v>24.1</v>
       </c>
       <c r="V28" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="W28" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y28" t="n">
         <v>4.7</v>
@@ -5462,22 +5529,22 @@
         <v>19.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.4</v>
+        <v>102.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
         <v>9</v>
       </c>
       <c r="AF28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG28" t="n">
         <v>9</v>
@@ -5501,13 +5568,13 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
         <v>7</v>
@@ -5522,10 +5589,10 @@
         <v>16</v>
       </c>
       <c r="AU28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
         <v>13</v>
@@ -5540,7 +5607,7 @@
         <v>11</v>
       </c>
       <c r="BA28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB28" t="n">
         <v>11</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E29" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F29" t="n">
         <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>0.603</v>
+        <v>0.597</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5593,31 +5660,31 @@
         <v>38.1</v>
       </c>
       <c r="J29" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L29" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>25.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="O29" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="P29" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="R29" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S29" t="n">
         <v>30.7</v>
@@ -5641,7 +5708,7 @@
         <v>5.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA29" t="n">
         <v>20.6</v>
@@ -5653,10 +5720,10 @@
         <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF29" t="n">
         <v>10</v>
@@ -5665,7 +5732,7 @@
         <v>10</v>
       </c>
       <c r="AH29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI29" t="n">
         <v>10</v>
@@ -5686,13 +5753,13 @@
         <v>14</v>
       </c>
       <c r="AO29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR29" t="n">
         <v>15</v>
@@ -5701,7 +5768,7 @@
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU29" t="n">
         <v>21</v>
@@ -5713,7 +5780,7 @@
         <v>15</v>
       </c>
       <c r="AX29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY29" t="n">
         <v>19</v>
@@ -5722,13 +5789,13 @@
         <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB29" t="n">
         <v>5</v>
       </c>
       <c r="BC29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E30" t="n">
         <v>30</v>
       </c>
       <c r="F30" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G30" t="n">
-        <v>0.448</v>
+        <v>0.455</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
@@ -5775,10 +5842,10 @@
         <v>35.5</v>
       </c>
       <c r="J30" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="K30" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L30" t="n">
         <v>7.3</v>
@@ -5787,7 +5854,7 @@
         <v>21</v>
       </c>
       <c r="N30" t="n">
-        <v>0.346</v>
+        <v>0.349</v>
       </c>
       <c r="O30" t="n">
         <v>16.7</v>
@@ -5796,22 +5863,22 @@
         <v>23</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.725</v>
+        <v>0.729</v>
       </c>
       <c r="R30" t="n">
         <v>11.9</v>
       </c>
       <c r="S30" t="n">
-        <v>32</v>
+        <v>32.2</v>
       </c>
       <c r="T30" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U30" t="n">
         <v>20.1</v>
       </c>
       <c r="V30" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W30" t="n">
         <v>7.2</v>
@@ -5820,7 +5887,7 @@
         <v>6</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z30" t="n">
         <v>19</v>
@@ -5829,22 +5896,22 @@
         <v>19.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH30" t="n">
         <v>30</v>
@@ -5865,7 +5932,7 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO30" t="n">
         <v>18</v>
@@ -5877,13 +5944,13 @@
         <v>25</v>
       </c>
       <c r="AR30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AT30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU30" t="n">
         <v>29</v>
@@ -5892,19 +5959,19 @@
         <v>26</v>
       </c>
       <c r="AW30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX30" t="n">
         <v>3</v>
       </c>
       <c r="AY30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ30" t="n">
         <v>7</v>
       </c>
       <c r="BA30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB30" t="n">
         <v>26</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E31" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F31" t="n">
         <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>0.588</v>
+        <v>0.582</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
       </c>
       <c r="I31" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="J31" t="n">
-        <v>82.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.468</v>
+        <v>0.467</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
@@ -5969,40 +6036,40 @@
         <v>16.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.363</v>
+        <v>0.361</v>
       </c>
       <c r="O31" t="n">
         <v>15.8</v>
       </c>
       <c r="P31" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Q31" t="n">
         <v>0.743</v>
       </c>
       <c r="R31" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S31" t="n">
         <v>33.6</v>
       </c>
       <c r="T31" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U31" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="V31" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W31" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z31" t="n">
         <v>21.1</v>
@@ -6011,13 +6078,13 @@
         <v>19.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.59999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6029,13 +6096,13 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ31" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK31" t="n">
         <v>3</v>
@@ -6065,19 +6132,19 @@
         <v>8</v>
       </c>
       <c r="AT31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW31" t="n">
         <v>19</v>
       </c>
       <c r="AX31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-18-2014-15</t>
+          <t>2015-03-18</t>
         </is>
       </c>
     </row>
